--- a/app/src/main/assets/Chinese_CAP_Quiz.xlsx
+++ b/app/src/main/assets/Chinese_CAP_Quiz.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Momo\AndroidStudioProjects\QuizHero\app\src\main\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFA652F3-E3CD-4331-A9EF-F08D9F9E123D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0793502D-BBF4-4C9A-9E17-3D8450888DB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{44B3D112-E0BA-4F81-A4DD-EBA0CE680863}"/>
   </bookViews>
@@ -28,28 +28,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="255">
-  <si>
-    <t>ID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SUB</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="254">
   <si>
     <t>VOL</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CHA</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ANS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>QUE</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -85,39 +69,21 @@
     <t xml:space="preserve">下列選項「　」中的字，何者讀音前後相同？　 (A). 青雲直「上」／平「上」去入　  (B). 個性倔「強」／「強」弩之末　  (C ). 「伺」機而動／茶水「伺」候　  (D). 不堪負「荷」／「荷」槍實彈 </t>
   </si>
   <si>
-    <t>Ｄ</t>
-  </si>
-  <si>
     <t xml:space="preserve">「品格如同樹木，名聲如同樹影。我們常常考慮的是樹影，卻不知樹木才是根本。」這句話的含義，與下列何者最接近？　 (A). 品格高貴的人，維護美好名譽遠超過自己的生命　  (B). 品格決定人真正的價值，名譽不過是外在的評斷　  (C ). 品格是一個人的根本，而名譽是衡量品格的標準　  (D). 品格和名譽相輔相成，美譽會激勵自己提升品格 </t>
   </si>
   <si>
-    <t xml:space="preserve">Ｂ </t>
-  </si>
-  <si>
     <t xml:space="preserve">「勺子裡的水閃光，海水卻是深暗的。渺小的道理可以明言，偉大的真理只有偉大的緘默。」這句話的含義與下列何者最接近？　 (A). 明者遠見於未萌，智者避危於無形　  (B). 量不寬不能容眾，識不明不堪大用　  (C ). 天地有大美而不言，萬物有成理而不說　  (D). 激湍之下必有深潭，高丘之下必有淵谷 </t>
   </si>
   <si>
-    <t>Ｃ</t>
-  </si>
-  <si>
     <t xml:space="preserve">「往昔，水鳥神祕的遷徙行為以及按時南北漂泊的生活一直使我著迷。完成觀察後，看到原本要設立保育區的沼澤繼續遭受破壞，我好像是做錯事一樣，再也不願去涉足。幸好還有溪澗可以慰藉，只是它又能維持多久？我的同胞們最懂得利用自然的一草一木了，總有一天他們也會完全開發這裡。與鳥一樣，我將被趕得無處可去。」根據本文，下列何者最符合作者的想法？　 (A). 對自然生態與環境的未來感到憂慮　  (B). 呼籲人們遠離高度開發的文明世界　  (C ). 為自己曾破壞自然保育區深感內疚　  (D). 感嘆己身如水鳥遷徙般漂泊的命運 </t>
   </si>
   <si>
-    <t>Ａ</t>
-  </si>
-  <si>
     <t xml:space="preserve">「窗前這幾片樹葉，使我感到造物者的智慧、細心。祂以大筆寫意，為我們描出了高山長水，而又如此的心思細膩，連幾片小小的木葉，都不掉以輕心，都仔細地予以賦色、描繪，使我們在生活中處處發現美的痕跡。我進而領悟：人人皆應師法這位偉大的畫師，一筆不苟，使人生的畫布無一漏筆或是敗筆。」根據這段文字，作者由樹葉所領悟的道理，與下列何者最接近？　 (A). 生命本是豐富而多元，歷練多了，生命也將變得多采多姿　  (B). 人應當秉持認真嚴謹的態度來經營生活，揮灑生命的色彩　  (C ). 繪畫是自然界與人類心靈的中介，人透過繪畫再現山水的面貌　  (D). 竭盡心力去感受美、追求美的人，美才會悄悄地進駐他的心扉 </t>
   </si>
   <si>
-    <t>Ｂ</t>
-  </si>
-  <si>
     <t xml:space="preserve"> (A).  (B).  (C ).  (D). </t>
   </si>
   <si>
-    <t xml:space="preserve">Ａ </t>
-  </si>
-  <si>
     <t xml:space="preserve">下列詞語「　」中的字，哪一組前後讀音相同？　 (A). 令人「咋」舌／「乍」看之下　  (B). 含「氟」牙膏／春風「拂」面　  (C ). 「匍」伏前進／灌溉花「圃」　  (D). 滿目「瘡」痍／「愴」然涕下 </t>
   </si>
   <si>
@@ -136,9 +102,6 @@
     <t xml:space="preserve">「自然界中，在透明度較高的水清水域，通常硝酸鹽、磷酸鹽等營養鹽的含量較少，相反地水濁時含量較多。營養鹽一旦缺乏，植物性浮游生物就發育不好，以它維生的動物性浮游生物就會變少，連帶影響取食動物性浮游生物的小魚和取食小魚的大型魚的生存。」根據這段文字，下列推論何者正確？　 (A). 水域混濁時，大魚數量會減少　  (B). 水域清澈時，浮游生物容易繁殖　  (C ). 在浮游生物多的水域中，魚類較容易生存　  (D). 同一水域中，動物性與植物性浮游生物的多寡成反比 </t>
   </si>
   <si>
-    <t xml:space="preserve">Ｃ </t>
-  </si>
-  <si>
     <t xml:space="preserve">「孫堅夫人吳氏，孕而夢月入懷，已而生策。及權在孕，又夢日入懷。以告堅曰：『妾昔懷策，夢月入懷。今又夢日，何也？』堅曰：『日月者，陰陽之精，極貴之象。吾子孫其興乎？』」根據文中人物的關係，下列說明何者正確？　 (A). 孫堅對孫策自稱「尊翁」　  (B). 孫權對孫策自稱為「愚兄」　  (C ). 孫策對他人稱吳氏為「家母」　  (D). 他人稱孫策與孫權為「賢喬梓」 </t>
   </si>
   <si>
@@ -205,9 +168,6 @@
     <t xml:space="preserve">「落帆逗淮鎮，停舫臨孤驛。浩浩風起波，冥冥日沉夕。人歸山郭暗，雁下蘆洲白。獨夜憶秦關，聽鐘未眠客。」關於這首詩的分析，下列敘述何者最恰當？　 (A). 首兩句寫出與友餞別的地點與時間　  (B). 以「風起」、「日沉」自喻懷才不遇　  (C ). 以「雁下蘆洲白」表示太陽將升起　  (D). 末兩句點出客因心有所思而不成眠 </t>
   </si>
   <si>
-    <t xml:space="preserve">Ｄ </t>
-  </si>
-  <si>
     <t xml:space="preserve">弘一大師覺得世間沒有不好的東西，即使所用之物已舊、所食之物平凡，卻什麼都有味，什麼都了不得；他咀嚼玩味日常事物，並從中得到樂趣。由此可知，弘一大師的生活態度與下列哪一句話最接近？　 (A). 不必占有，只要純粹欣賞美的事物便能感到快樂　  (B). 接受自己、忠於自己，並以同樣的態度對待他人　  (C ). 知足常樂的祕訣在於懂得珍惜眼前所有、當下所遇　  (D). 生命貴在顯露自己真實的情感，展現對生活的熱情 </t>
   </si>
   <si>
@@ -403,9 +363,6 @@
     <t xml:space="preserve">「我慶幸自己不是權力之輪，而是任其輾過的眾生之一。」這句話的涵義，與下列何者最接近？　 (A). 寧可因循的苟活，也不要大起大落，橫生波折　  (B). 就算被踐踏壓迫，也不願擁有權勢，欺凌他人　  (C ). 受折磨雖然痛苦，但卻能砥礪心性，超脫自我　  (D). 不一定非要掌權，才能夠開創新局，造福眾生 </t>
   </si>
   <si>
-    <t xml:space="preserve">下列「　」中的字音，何者前後相同？　 (A). 陰「霾」的天氣令人心情鬱悶／果子「貍」被懷疑帶有ＳＡＲＳ的病原體　  (B). 多吃高「纖」蔬果，有益身體健康／上臺表演的順序以抽「籤」方式來決定　  (C ). 一早進來，老師和「藹」的笑容照亮了教室／濛濛暮「靄」，遮蔽了黃昏的天際　  (D). 心情煩躁的他忍不住對屬下「咆」哮／天空的水蒸氣遇冷結冰，成塊下降，稱為冰「雹」 </t>
-  </si>
-  <si>
     <t xml:space="preserve">「考期將至，望著桌上堆積如山的書本，我的心在瞬間彷彿變成了鉛塊。當下只有悔恨，悔恨自己未能善加運用時間。」作者在句中以「鉛塊」來比喻他當下的哪一種心情？　 (A). 煩躁　  (B). 堅定　  (C ). 麻木　  (D). 沉重 </t>
   </si>
   <si>
@@ -442,9 +399,6 @@
     <t xml:space="preserve">在外地求學的郭襄，想寫明信片給她的姐姐郭芙。下圖明信片的格式中，（甲）、（乙）處依序應填入下列何者？   (A). 郭襄　緘／郭芙　吾姐　啟　  (B). 郭襄　寄／郭芙　小姐　收　  (C ). 郭襄　緘／郭芙　小姐　臺啟　  (D). 郭襄　寄／郭芙　吾姐　敬收 </t>
   </si>
   <si>
-    <t xml:space="preserve">以下圖表，是某年經濟合作與發展組織（ＯＥＣＤ）針對各國各階段教育每人所分得經費的調查結果：_x0001_根據這張圖表，下列敘述何者正確？　 (A). 甲國小學生所分得的教育經費高於ＯＥＣＤ調查平均值　  (B). 丙國國中生所分得的教育經費高於ＯＥＣＤ調查平均值　  (C ). 各國高等教育學生所分得的經費皆多於其他階段學生　  (D). 相較於其他國家，丁國高中生所分得的教育經費最高 </t>
-  </si>
-  <si>
     <t xml:space="preserve">小敬搬新家，阿嬌欲送禮金表達祝賀之意。下列題辭，何者最適合寫在賀儀封套上？　 (A). 近悅遠來　  (B). 造福桑梓　  (C ). 宜室宜家　  (D). 喬遷之喜 </t>
   </si>
   <si>
@@ -793,9 +747,6 @@
     <t xml:space="preserve">「海上垃圾桶的概念始於兩位衝浪者，他們在世界各地目睹聚集在碼頭的大量汙染物，故而想改善這個現象。海上垃圾桶是由大型纖維網製成，架設於碼頭附近且漂在海面上，以收集不同尺寸的汙染物，最小可攔住直徑２ｍｍ的浮動碎屑，當發生溢油事件時，也能派上極大的用場。」依據這段文字，下列關於海上垃圾桶的作用何者正確？　 (A). 收集海底的垃圾　  (B). 預防溢油事件發生　  (C ). 攔截沿海的汙染物　  (D). 清除所有尺寸的垃圾 </t>
   </si>
   <si>
-    <t xml:space="preserve">下列四句話的文字與標點符號稍有差異，何者含意與其他三者相差最遠？　 (A). 哆啦Ａ夢說他要帶大雄去暢遊未來世界。　  (B). 哆啦Ａ夢說：「他要帶大雄去暢遊未來世界。」　  (C ). 哆啦Ａ夢說：「我要帶大雄去暢遊未來世界。」　  (D). 哆啦Ａ夢告訴大雄：「我要帶你去暢遊未來世界 </t>
-  </si>
-  <si>
     <t xml:space="preserve">  根據這張圖表，下列何者的症狀最可能是中暑？　 (A). 冒汗而體溫正常的小健　  (B). 體溫過高不出汗的小康　  (C ). 大量流汗虛弱頭暈的小平　  (D). 心跳加速體溫正常的小安 </t>
   </si>
   <si>
@@ -806,6 +757,48 @@
   </si>
   <si>
     <t xml:space="preserve">「朋友曾問過我一個問題□失去視力和失去聽力，害怕哪一項？我思考許久，最後坦承：什麼也不想失去。眼睛的世界那樣可喜，聽見的聲音卻更像一種心靈的共振□閉上眼睛也能讓情節自己呼應。我不能放棄兩者□也不願被兩者放棄。」這段文字空格處的標點符號，依序填入下列何者最恰當？　 (A). ， 。 ；　  (B). ， ； 、　  (C ). ： ， ，　  (D). ：  </t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>SUB</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B </t>
+  </si>
+  <si>
+    <t>CHA</t>
+  </si>
+  <si>
+    <t>ANS</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">下列四句話的文字與標點符號稍有差異，何者含意與其他三者相差最遠？　 (A). 哆啦A夢說他要帶大雄去暢遊未來世界。　  (B). 哆啦A夢說：「他要帶大雄去暢遊未來世界。」　  (C ). 哆啦A夢說：「我要帶大雄去暢遊未來世界。」　  (D). 哆啦A夢告訴大雄：「我要帶你去暢遊未來世界 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">A </t>
+  </si>
+  <si>
+    <t xml:space="preserve">下列「　」中的字音，何者前後相同？　 (A). 陰「霾」的天氣令人心情鬱悶／果子「貍」被懷疑帶有ＳAＲＳ的病原體　  (B). 多吃高「纖」蔬果，有益身體健康／上臺表演的順序以抽「籤」方式來決定　  (C ). 一早進來，老師和「藹」的笑容照亮了教室／濛濛暮「靄」，遮蔽了黃昏的天際　  (D). 心情煩躁的他忍不住對屬下「咆」哮／天空的水蒸氣遇冷結冰，成塊下降，稱為冰「雹」 </t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D </t>
+  </si>
+  <si>
+    <t xml:space="preserve">以下圖表，是某年經濟合作與發展組織（ＯＥCD）針對各國各階段教育每人所分得經費的調查結果：_x0001_根據這張圖表，下列敘述何者正確？　 (A). 甲國小學生所分得的教育經費高於ＯＥCD調查平均值　  (B). 丙國國中生所分得的教育經費高於ＯＥCD調查平均值　  (C ). 各國高等教育學生所分得的經費皆多於其他階段學生　  (D). 相較於其他國家，丁國高中生所分得的教育經費最高 </t>
   </si>
 </sst>
 </file>
@@ -1199,43 +1192,43 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B1" t="s">
+        <v>241</v>
+      </c>
+      <c r="C1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
+        <v>244</v>
+      </c>
+      <c r="E1" t="s">
+        <v>245</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="H1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="I1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="J1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="K1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="L1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="M1" t="s">
         <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.45">
@@ -1252,10 +1245,10 @@
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>31</v>
+        <v>240</v>
       </c>
       <c r="F2" t="s">
-        <v>254</v>
+        <v>239</v>
       </c>
       <c r="G2" s="1"/>
     </row>
@@ -1273,10 +1266,10 @@
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>242</v>
       </c>
       <c r="F3" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="G3" s="1"/>
     </row>
@@ -1294,10 +1287,10 @@
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>246</v>
       </c>
       <c r="F4" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="G4" s="1"/>
     </row>
@@ -1315,10 +1308,10 @@
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>16</v>
+        <v>243</v>
       </c>
       <c r="F5" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="G5" s="1"/>
     </row>
@@ -1336,10 +1329,10 @@
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>22</v>
+        <v>242</v>
       </c>
       <c r="F6" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G6" s="1"/>
     </row>
@@ -1357,10 +1350,10 @@
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>31</v>
+        <v>240</v>
       </c>
       <c r="F7" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
       <c r="G7" s="1"/>
     </row>
@@ -1378,10 +1371,10 @@
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>16</v>
+        <v>243</v>
       </c>
       <c r="F8" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G8" s="1"/>
     </row>
@@ -1399,10 +1392,10 @@
         <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>20</v>
+        <v>246</v>
       </c>
       <c r="F9" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="G9" s="1"/>
     </row>
@@ -1420,10 +1413,10 @@
         <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>18</v>
+        <v>240</v>
       </c>
       <c r="F10" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="G10" s="1"/>
     </row>
@@ -1441,10 +1434,10 @@
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>20</v>
+        <v>246</v>
       </c>
       <c r="F11" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="G11" s="1"/>
     </row>
@@ -1462,10 +1455,10 @@
         <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>31</v>
+        <v>240</v>
       </c>
       <c r="F12" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="G12" s="1"/>
     </row>
@@ -1483,10 +1476,10 @@
         <v>1</v>
       </c>
       <c r="E13" t="s">
-        <v>20</v>
+        <v>246</v>
       </c>
       <c r="F13" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="G13" s="1"/>
     </row>
@@ -1504,10 +1497,10 @@
         <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>14</v>
+        <v>251</v>
       </c>
       <c r="F14" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="G14" s="1"/>
     </row>
@@ -1525,10 +1518,10 @@
         <v>1</v>
       </c>
       <c r="E15" t="s">
-        <v>54</v>
+        <v>252</v>
       </c>
       <c r="F15" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="G15" s="1"/>
     </row>
@@ -1546,10 +1539,10 @@
         <v>1</v>
       </c>
       <c r="E16" t="s">
-        <v>31</v>
+        <v>240</v>
       </c>
       <c r="F16" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="G16" s="1"/>
     </row>
@@ -1567,10 +1560,10 @@
         <v>1</v>
       </c>
       <c r="E17" t="s">
-        <v>24</v>
+        <v>248</v>
       </c>
       <c r="F17" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="G17" s="1"/>
     </row>
@@ -1588,10 +1581,10 @@
         <v>1</v>
       </c>
       <c r="E18" t="s">
-        <v>16</v>
+        <v>243</v>
       </c>
       <c r="F18" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="G18" s="1"/>
     </row>
@@ -1609,10 +1602,10 @@
         <v>1</v>
       </c>
       <c r="E19" t="s">
-        <v>24</v>
+        <v>248</v>
       </c>
       <c r="F19" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
       <c r="G19" s="1"/>
     </row>
@@ -1630,10 +1623,10 @@
         <v>1</v>
       </c>
       <c r="E20" t="s">
-        <v>24</v>
+        <v>248</v>
       </c>
       <c r="F20" t="s">
-        <v>236</v>
+        <v>222</v>
       </c>
       <c r="G20" s="1"/>
     </row>
@@ -1651,10 +1644,10 @@
         <v>1</v>
       </c>
       <c r="E21" t="s">
-        <v>31</v>
+        <v>240</v>
       </c>
       <c r="F21" t="s">
-        <v>235</v>
+        <v>221</v>
       </c>
       <c r="G21" s="1"/>
     </row>
@@ -1672,10 +1665,10 @@
         <v>1</v>
       </c>
       <c r="E22" t="s">
-        <v>54</v>
+        <v>252</v>
       </c>
       <c r="F22" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="G22" s="1"/>
     </row>
@@ -1693,10 +1686,10 @@
         <v>1</v>
       </c>
       <c r="E23" t="s">
-        <v>22</v>
+        <v>242</v>
       </c>
       <c r="F23" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="G23" s="1"/>
     </row>
@@ -1714,10 +1707,10 @@
         <v>1</v>
       </c>
       <c r="E24" t="s">
-        <v>14</v>
+        <v>251</v>
       </c>
       <c r="F24" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="G24" s="1"/>
     </row>
@@ -1735,10 +1728,10 @@
         <v>1</v>
       </c>
       <c r="E25" t="s">
-        <v>22</v>
+        <v>242</v>
       </c>
       <c r="F25" t="s">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="G25" s="1"/>
     </row>
@@ -1756,10 +1749,10 @@
         <v>1</v>
       </c>
       <c r="E26" t="s">
-        <v>24</v>
+        <v>248</v>
       </c>
       <c r="F26" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="G26" s="1"/>
     </row>
@@ -1777,10 +1770,10 @@
         <v>1</v>
       </c>
       <c r="E27" t="s">
-        <v>18</v>
+        <v>240</v>
       </c>
       <c r="F27" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="G27" s="1"/>
     </row>
@@ -1798,10 +1791,10 @@
         <v>1</v>
       </c>
       <c r="E28" t="s">
-        <v>18</v>
+        <v>240</v>
       </c>
       <c r="F28" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="G28" s="1"/>
     </row>
@@ -1819,10 +1812,10 @@
         <v>1</v>
       </c>
       <c r="E29" t="s">
-        <v>16</v>
+        <v>243</v>
       </c>
       <c r="F29" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="G29" s="1"/>
     </row>
@@ -1840,10 +1833,10 @@
         <v>1</v>
       </c>
       <c r="E30" t="s">
-        <v>24</v>
+        <v>248</v>
       </c>
       <c r="F30" t="s">
-        <v>226</v>
+        <v>212</v>
       </c>
       <c r="G30" s="1"/>
     </row>
@@ -1861,10 +1854,10 @@
         <v>1</v>
       </c>
       <c r="E31" t="s">
-        <v>22</v>
+        <v>242</v>
       </c>
       <c r="F31" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="G31" s="1"/>
     </row>
@@ -1882,10 +1875,10 @@
         <v>1</v>
       </c>
       <c r="E32" t="s">
-        <v>22</v>
+        <v>242</v>
       </c>
       <c r="F32" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="G32" s="1"/>
     </row>
@@ -1903,10 +1896,10 @@
         <v>1</v>
       </c>
       <c r="E33" t="s">
-        <v>22</v>
+        <v>242</v>
       </c>
       <c r="F33" t="s">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="G33" s="1"/>
     </row>
@@ -1924,10 +1917,10 @@
         <v>1</v>
       </c>
       <c r="E34" t="s">
-        <v>22</v>
+        <v>242</v>
       </c>
       <c r="F34" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="G34" s="1"/>
     </row>
@@ -1945,10 +1938,10 @@
         <v>1</v>
       </c>
       <c r="E35" t="s">
-        <v>54</v>
+        <v>252</v>
       </c>
       <c r="F35" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G35" s="1"/>
     </row>
@@ -1966,10 +1959,10 @@
         <v>1</v>
       </c>
       <c r="E36" t="s">
-        <v>20</v>
+        <v>246</v>
       </c>
       <c r="F36" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="G36" s="1"/>
     </row>
@@ -1987,10 +1980,10 @@
         <v>1</v>
       </c>
       <c r="E37" t="s">
-        <v>31</v>
+        <v>240</v>
       </c>
       <c r="F37" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="G37" s="1"/>
     </row>
@@ -2008,10 +2001,10 @@
         <v>1</v>
       </c>
       <c r="E38" t="s">
-        <v>54</v>
+        <v>252</v>
       </c>
       <c r="F38" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="G38" s="1"/>
     </row>
@@ -2029,10 +2022,10 @@
         <v>1</v>
       </c>
       <c r="E39" t="s">
-        <v>20</v>
+        <v>246</v>
       </c>
       <c r="F39" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="G39" s="1"/>
     </row>
@@ -2050,10 +2043,10 @@
         <v>1</v>
       </c>
       <c r="E40" t="s">
-        <v>16</v>
+        <v>243</v>
       </c>
       <c r="F40" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="G40" s="1"/>
     </row>
@@ -2071,10 +2064,10 @@
         <v>1</v>
       </c>
       <c r="E41" t="s">
-        <v>54</v>
+        <v>252</v>
       </c>
       <c r="F41" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="G41" s="1"/>
     </row>
@@ -2092,10 +2085,10 @@
         <v>1</v>
       </c>
       <c r="E42" t="s">
-        <v>14</v>
+        <v>251</v>
       </c>
       <c r="F42" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="G42" s="1"/>
     </row>
@@ -2113,10 +2106,10 @@
         <v>1</v>
       </c>
       <c r="E43" t="s">
-        <v>54</v>
+        <v>252</v>
       </c>
       <c r="F43" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="G43" s="1"/>
     </row>
@@ -2134,10 +2127,10 @@
         <v>1</v>
       </c>
       <c r="E44" t="s">
-        <v>22</v>
+        <v>242</v>
       </c>
       <c r="F44" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="G44" s="1"/>
     </row>
@@ -2155,10 +2148,10 @@
         <v>1</v>
       </c>
       <c r="E45" t="s">
-        <v>14</v>
+        <v>251</v>
       </c>
       <c r="F45" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="G45" s="1"/>
     </row>
@@ -2176,10 +2169,10 @@
         <v>1</v>
       </c>
       <c r="E46" t="s">
-        <v>16</v>
+        <v>243</v>
       </c>
       <c r="F46" t="s">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="G46" s="1"/>
     </row>
@@ -2197,10 +2190,10 @@
         <v>1</v>
       </c>
       <c r="E47" t="s">
-        <v>16</v>
+        <v>243</v>
       </c>
       <c r="F47" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="G47" s="1"/>
     </row>
@@ -2218,10 +2211,10 @@
         <v>1</v>
       </c>
       <c r="E48" t="s">
-        <v>31</v>
+        <v>240</v>
       </c>
       <c r="F48" t="s">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="G48" s="1"/>
     </row>
@@ -2239,10 +2232,10 @@
         <v>1</v>
       </c>
       <c r="E49" t="s">
-        <v>54</v>
+        <v>252</v>
       </c>
       <c r="F49" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="G49" s="1"/>
     </row>
@@ -2260,10 +2253,10 @@
         <v>1</v>
       </c>
       <c r="E50" t="s">
-        <v>18</v>
+        <v>240</v>
       </c>
       <c r="F50" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="G50" s="1"/>
     </row>
@@ -2281,10 +2274,10 @@
         <v>1</v>
       </c>
       <c r="E51" t="s">
-        <v>14</v>
+        <v>251</v>
       </c>
       <c r="F51" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="G51" s="1"/>
     </row>
@@ -2302,10 +2295,10 @@
         <v>1</v>
       </c>
       <c r="E52" t="s">
-        <v>24</v>
+        <v>248</v>
       </c>
       <c r="F52" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="G52" s="1"/>
     </row>
@@ -2323,10 +2316,10 @@
         <v>1</v>
       </c>
       <c r="E53" t="s">
-        <v>24</v>
+        <v>248</v>
       </c>
       <c r="F53" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="G53" s="1"/>
     </row>
@@ -2344,10 +2337,10 @@
         <v>1</v>
       </c>
       <c r="E54" t="s">
-        <v>14</v>
+        <v>251</v>
       </c>
       <c r="F54" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="G54" s="1"/>
     </row>
@@ -2365,10 +2358,10 @@
         <v>1</v>
       </c>
       <c r="E55" t="s">
-        <v>20</v>
+        <v>246</v>
       </c>
       <c r="F55" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="G55" s="1"/>
     </row>
@@ -2386,10 +2379,10 @@
         <v>1</v>
       </c>
       <c r="E56" t="s">
-        <v>22</v>
+        <v>242</v>
       </c>
       <c r="F56" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="G56" s="1"/>
     </row>
@@ -2407,10 +2400,10 @@
         <v>1</v>
       </c>
       <c r="E57" t="s">
-        <v>22</v>
+        <v>242</v>
       </c>
       <c r="F57" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="G57" s="1"/>
     </row>
@@ -2428,10 +2421,10 @@
         <v>1</v>
       </c>
       <c r="E58" t="s">
-        <v>16</v>
+        <v>243</v>
       </c>
       <c r="F58" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="G58" s="1"/>
     </row>
@@ -2449,10 +2442,10 @@
         <v>1</v>
       </c>
       <c r="E59" t="s">
-        <v>22</v>
+        <v>242</v>
       </c>
       <c r="F59" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="G59" s="1"/>
     </row>
@@ -2470,10 +2463,10 @@
         <v>1</v>
       </c>
       <c r="E60" t="s">
-        <v>16</v>
+        <v>243</v>
       </c>
       <c r="F60" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="G60" s="1"/>
     </row>
@@ -2491,10 +2484,10 @@
         <v>1</v>
       </c>
       <c r="E61" t="s">
-        <v>20</v>
+        <v>246</v>
       </c>
       <c r="F61" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="G61" s="1"/>
     </row>
@@ -2512,10 +2505,10 @@
         <v>1</v>
       </c>
       <c r="E62" t="s">
-        <v>20</v>
+        <v>246</v>
       </c>
       <c r="F62" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="G62" s="1"/>
     </row>
@@ -2533,10 +2526,10 @@
         <v>1</v>
       </c>
       <c r="E63" t="s">
-        <v>22</v>
+        <v>242</v>
       </c>
       <c r="F63" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="G63" s="1"/>
     </row>
@@ -2554,10 +2547,10 @@
         <v>1</v>
       </c>
       <c r="E64" t="s">
-        <v>31</v>
+        <v>240</v>
       </c>
       <c r="F64" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="G64" s="1"/>
     </row>
@@ -2575,10 +2568,10 @@
         <v>1</v>
       </c>
       <c r="E65" t="s">
-        <v>20</v>
+        <v>246</v>
       </c>
       <c r="F65" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="G65" s="1"/>
     </row>
@@ -2596,10 +2589,10 @@
         <v>1</v>
       </c>
       <c r="E66" t="s">
-        <v>54</v>
+        <v>252</v>
       </c>
       <c r="F66" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="G66" s="1"/>
     </row>
@@ -2617,10 +2610,10 @@
         <v>1</v>
       </c>
       <c r="E67" t="s">
-        <v>16</v>
+        <v>243</v>
       </c>
       <c r="F67" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="G67" s="1"/>
     </row>
@@ -2638,10 +2631,10 @@
         <v>1</v>
       </c>
       <c r="E68" t="s">
-        <v>54</v>
+        <v>252</v>
       </c>
       <c r="F68" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="G68" s="1"/>
     </row>
@@ -2659,10 +2652,10 @@
         <v>1</v>
       </c>
       <c r="E69" t="s">
-        <v>16</v>
+        <v>243</v>
       </c>
       <c r="F69" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="G69" s="1"/>
     </row>
@@ -2680,10 +2673,10 @@
         <v>1</v>
       </c>
       <c r="E70" t="s">
-        <v>31</v>
+        <v>240</v>
       </c>
       <c r="F70" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="G70" s="1"/>
     </row>
@@ -2701,10 +2694,10 @@
         <v>1</v>
       </c>
       <c r="E71" t="s">
-        <v>31</v>
+        <v>240</v>
       </c>
       <c r="F71" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="G71" s="1"/>
     </row>
@@ -2722,10 +2715,10 @@
         <v>1</v>
       </c>
       <c r="E72" t="s">
-        <v>18</v>
+        <v>240</v>
       </c>
       <c r="F72" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="G72" s="1"/>
     </row>
@@ -2743,10 +2736,10 @@
         <v>1</v>
       </c>
       <c r="E73" t="s">
-        <v>22</v>
+        <v>242</v>
       </c>
       <c r="F73" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="G73" s="1"/>
     </row>
@@ -2764,10 +2757,10 @@
         <v>1</v>
       </c>
       <c r="E74" t="s">
-        <v>18</v>
+        <v>240</v>
       </c>
       <c r="F74" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="G74" s="1"/>
     </row>
@@ -2785,10 +2778,10 @@
         <v>1</v>
       </c>
       <c r="E75" t="s">
-        <v>14</v>
+        <v>251</v>
       </c>
       <c r="F75" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="G75" s="1"/>
     </row>
@@ -2806,10 +2799,10 @@
         <v>1</v>
       </c>
       <c r="E76" t="s">
-        <v>20</v>
+        <v>246</v>
       </c>
       <c r="F76" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="G76" s="1"/>
     </row>
@@ -2827,10 +2820,10 @@
         <v>1</v>
       </c>
       <c r="E77" t="s">
-        <v>22</v>
+        <v>242</v>
       </c>
       <c r="F77" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="G77" s="1"/>
     </row>
@@ -2848,10 +2841,10 @@
         <v>1</v>
       </c>
       <c r="E78" t="s">
-        <v>14</v>
+        <v>251</v>
       </c>
       <c r="F78" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G78" s="1"/>
     </row>
@@ -2869,10 +2862,10 @@
         <v>1</v>
       </c>
       <c r="E79" t="s">
-        <v>20</v>
+        <v>246</v>
       </c>
       <c r="F79" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="G79" s="1"/>
     </row>
@@ -2890,10 +2883,10 @@
         <v>1</v>
       </c>
       <c r="E80" t="s">
-        <v>54</v>
+        <v>252</v>
       </c>
       <c r="F80" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="G80" s="1"/>
     </row>
@@ -2911,10 +2904,10 @@
         <v>1</v>
       </c>
       <c r="E81" t="s">
-        <v>14</v>
+        <v>251</v>
       </c>
       <c r="F81" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="G81" s="1"/>
     </row>
@@ -2932,10 +2925,10 @@
         <v>1</v>
       </c>
       <c r="E82" t="s">
-        <v>31</v>
+        <v>240</v>
       </c>
       <c r="F82" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="G82" s="1"/>
     </row>
@@ -2953,10 +2946,10 @@
         <v>1</v>
       </c>
       <c r="E83" t="s">
-        <v>20</v>
+        <v>246</v>
       </c>
       <c r="F83" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="G83" s="1"/>
     </row>
@@ -2974,10 +2967,10 @@
         <v>1</v>
       </c>
       <c r="E84" t="s">
-        <v>24</v>
+        <v>248</v>
       </c>
       <c r="F84" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="G84" s="1"/>
     </row>
@@ -2995,10 +2988,10 @@
         <v>1</v>
       </c>
       <c r="E85" t="s">
-        <v>20</v>
+        <v>246</v>
       </c>
       <c r="F85" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="G85" s="1"/>
     </row>
@@ -3016,10 +3009,10 @@
         <v>1</v>
       </c>
       <c r="E86" t="s">
-        <v>54</v>
+        <v>252</v>
       </c>
       <c r="F86" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="G86" s="1"/>
     </row>
@@ -3037,10 +3030,10 @@
         <v>1</v>
       </c>
       <c r="E87" t="s">
-        <v>22</v>
+        <v>242</v>
       </c>
       <c r="F87" t="s">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="G87" s="1"/>
     </row>
@@ -3058,10 +3051,10 @@
         <v>1</v>
       </c>
       <c r="E88" t="s">
-        <v>16</v>
+        <v>243</v>
       </c>
       <c r="F88" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="G88" s="1"/>
     </row>
@@ -3079,10 +3072,10 @@
         <v>1</v>
       </c>
       <c r="E89" t="s">
-        <v>16</v>
+        <v>243</v>
       </c>
       <c r="F89" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="G89" s="1"/>
     </row>
@@ -3100,10 +3093,10 @@
         <v>1</v>
       </c>
       <c r="E90" t="s">
-        <v>14</v>
+        <v>251</v>
       </c>
       <c r="F90" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="G90" s="1"/>
     </row>
@@ -3121,10 +3114,10 @@
         <v>1</v>
       </c>
       <c r="E91" t="s">
-        <v>14</v>
+        <v>251</v>
       </c>
       <c r="F91" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="G91" s="1"/>
     </row>
@@ -3142,10 +3135,10 @@
         <v>1</v>
       </c>
       <c r="E92" t="s">
-        <v>24</v>
+        <v>248</v>
       </c>
       <c r="F92" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="G92" s="1"/>
     </row>
@@ -3163,10 +3156,10 @@
         <v>1</v>
       </c>
       <c r="E93" t="s">
-        <v>20</v>
+        <v>246</v>
       </c>
       <c r="F93" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="G93" s="1"/>
     </row>
@@ -3184,10 +3177,10 @@
         <v>1</v>
       </c>
       <c r="E94" t="s">
-        <v>20</v>
+        <v>246</v>
       </c>
       <c r="F94" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="G94" s="1"/>
     </row>
@@ -3205,10 +3198,10 @@
         <v>1</v>
       </c>
       <c r="E95" t="s">
-        <v>31</v>
+        <v>240</v>
       </c>
       <c r="F95" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="G95" s="1"/>
     </row>
@@ -3226,10 +3219,10 @@
         <v>1</v>
       </c>
       <c r="E96" t="s">
-        <v>31</v>
+        <v>240</v>
       </c>
       <c r="F96" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="G96" s="1"/>
     </row>
@@ -3247,10 +3240,10 @@
         <v>1</v>
       </c>
       <c r="E97" t="s">
-        <v>54</v>
+        <v>252</v>
       </c>
       <c r="F97" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="G97" s="1"/>
     </row>
@@ -3268,10 +3261,10 @@
         <v>1</v>
       </c>
       <c r="E98" t="s">
-        <v>24</v>
+        <v>248</v>
       </c>
       <c r="F98" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="G98" s="1"/>
     </row>
@@ -3289,10 +3282,10 @@
         <v>1</v>
       </c>
       <c r="E99" t="s">
-        <v>16</v>
+        <v>243</v>
       </c>
       <c r="F99" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="G99" s="1"/>
     </row>
@@ -3310,10 +3303,10 @@
         <v>1</v>
       </c>
       <c r="E100" t="s">
-        <v>18</v>
+        <v>240</v>
       </c>
       <c r="F100" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="G100" s="1"/>
     </row>
@@ -3331,10 +3324,10 @@
         <v>1</v>
       </c>
       <c r="E101" t="s">
-        <v>24</v>
+        <v>248</v>
       </c>
       <c r="F101" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="G101" s="1"/>
     </row>
@@ -3352,10 +3345,10 @@
         <v>1</v>
       </c>
       <c r="E102" t="s">
-        <v>14</v>
+        <v>251</v>
       </c>
       <c r="F102" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="G102" s="1"/>
     </row>
@@ -3373,10 +3366,10 @@
         <v>1</v>
       </c>
       <c r="E103" t="s">
-        <v>20</v>
+        <v>246</v>
       </c>
       <c r="F103" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="G103" s="1"/>
     </row>
@@ -3394,10 +3387,10 @@
         <v>1</v>
       </c>
       <c r="E104" t="s">
-        <v>24</v>
+        <v>248</v>
       </c>
       <c r="F104" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="G104" s="1"/>
     </row>
@@ -3415,10 +3408,10 @@
         <v>1</v>
       </c>
       <c r="E105" t="s">
-        <v>18</v>
+        <v>240</v>
       </c>
       <c r="F105" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="G105" s="1"/>
     </row>
@@ -3436,10 +3429,10 @@
         <v>1</v>
       </c>
       <c r="E106" t="s">
-        <v>18</v>
+        <v>240</v>
       </c>
       <c r="F106" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="G106" s="1"/>
     </row>
@@ -3457,10 +3450,10 @@
         <v>1</v>
       </c>
       <c r="E107" t="s">
-        <v>31</v>
+        <v>240</v>
       </c>
       <c r="F107" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="G107" s="1"/>
     </row>
@@ -3478,10 +3471,10 @@
         <v>1</v>
       </c>
       <c r="E108" t="s">
-        <v>22</v>
+        <v>242</v>
       </c>
       <c r="F108" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="G108" s="1"/>
     </row>
@@ -3499,10 +3492,10 @@
         <v>1</v>
       </c>
       <c r="E109" t="s">
-        <v>54</v>
+        <v>252</v>
       </c>
       <c r="F109" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="G109" s="1"/>
     </row>
@@ -3520,10 +3513,10 @@
         <v>1</v>
       </c>
       <c r="E110" t="s">
-        <v>31</v>
+        <v>240</v>
       </c>
       <c r="F110" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="G110" s="1"/>
     </row>
@@ -3541,10 +3534,10 @@
         <v>1</v>
       </c>
       <c r="E111" t="s">
-        <v>16</v>
+        <v>243</v>
       </c>
       <c r="F111" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="G111" s="1"/>
     </row>
@@ -3562,10 +3555,10 @@
         <v>1</v>
       </c>
       <c r="E112" t="s">
-        <v>20</v>
+        <v>246</v>
       </c>
       <c r="F112" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="G112" s="1"/>
     </row>
@@ -3583,10 +3576,10 @@
         <v>1</v>
       </c>
       <c r="E113" t="s">
-        <v>20</v>
+        <v>246</v>
       </c>
       <c r="F113" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="G113" s="1"/>
     </row>
@@ -3604,10 +3597,10 @@
         <v>1</v>
       </c>
       <c r="E114" t="s">
-        <v>20</v>
+        <v>246</v>
       </c>
       <c r="F114" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="G114" s="1"/>
     </row>
@@ -3625,10 +3618,10 @@
         <v>1</v>
       </c>
       <c r="E115" t="s">
-        <v>20</v>
+        <v>246</v>
       </c>
       <c r="F115" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="G115" s="1"/>
     </row>
@@ -3646,10 +3639,10 @@
         <v>1</v>
       </c>
       <c r="E116" t="s">
-        <v>54</v>
+        <v>252</v>
       </c>
       <c r="F116" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="G116" s="1"/>
     </row>
@@ -3667,10 +3660,10 @@
         <v>1</v>
       </c>
       <c r="E117" t="s">
-        <v>18</v>
+        <v>240</v>
       </c>
       <c r="F117" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="G117" s="1"/>
     </row>
@@ -3688,10 +3681,10 @@
         <v>1</v>
       </c>
       <c r="E118" t="s">
-        <v>16</v>
+        <v>243</v>
       </c>
       <c r="F118" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="G118" s="1"/>
     </row>
@@ -3709,10 +3702,10 @@
         <v>1</v>
       </c>
       <c r="E119" t="s">
-        <v>14</v>
+        <v>251</v>
       </c>
       <c r="F119" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="G119" s="1"/>
     </row>
@@ -3730,10 +3723,10 @@
         <v>1</v>
       </c>
       <c r="E120" t="s">
-        <v>18</v>
+        <v>240</v>
       </c>
       <c r="F120" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="G120" s="1"/>
     </row>
@@ -3751,10 +3744,10 @@
         <v>1</v>
       </c>
       <c r="E121" t="s">
-        <v>14</v>
+        <v>251</v>
       </c>
       <c r="F121" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="G121" s="1"/>
     </row>
@@ -3772,10 +3765,10 @@
         <v>1</v>
       </c>
       <c r="E122" t="s">
-        <v>54</v>
+        <v>252</v>
       </c>
       <c r="F122" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="G122" s="1"/>
     </row>
@@ -3793,10 +3786,10 @@
         <v>1</v>
       </c>
       <c r="E123" t="s">
-        <v>14</v>
+        <v>251</v>
       </c>
       <c r="F123" t="s">
-        <v>133</v>
+        <v>253</v>
       </c>
       <c r="G123" s="1"/>
     </row>
@@ -3814,10 +3807,10 @@
         <v>1</v>
       </c>
       <c r="E124" t="s">
-        <v>16</v>
+        <v>243</v>
       </c>
       <c r="F124" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="G124" s="1"/>
     </row>
@@ -3835,10 +3828,10 @@
         <v>1</v>
       </c>
       <c r="E125" t="s">
-        <v>24</v>
+        <v>248</v>
       </c>
       <c r="F125" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="G125" s="1"/>
     </row>
@@ -3856,10 +3849,10 @@
         <v>1</v>
       </c>
       <c r="E126" t="s">
-        <v>54</v>
+        <v>252</v>
       </c>
       <c r="F126" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="G126" s="1"/>
     </row>
@@ -3877,10 +3870,10 @@
         <v>1</v>
       </c>
       <c r="E127" t="s">
-        <v>20</v>
+        <v>246</v>
       </c>
       <c r="F127" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="G127" s="1"/>
     </row>
@@ -3898,10 +3891,10 @@
         <v>1</v>
       </c>
       <c r="E128" t="s">
-        <v>22</v>
+        <v>242</v>
       </c>
       <c r="F128" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="G128" s="1"/>
     </row>
@@ -3919,10 +3912,10 @@
         <v>1</v>
       </c>
       <c r="E129" t="s">
-        <v>54</v>
+        <v>252</v>
       </c>
       <c r="F129" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="G129" s="1"/>
     </row>
@@ -3940,10 +3933,10 @@
         <v>1</v>
       </c>
       <c r="E130" t="s">
-        <v>24</v>
+        <v>248</v>
       </c>
       <c r="F130" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="G130" s="1"/>
     </row>
@@ -3961,10 +3954,10 @@
         <v>1</v>
       </c>
       <c r="E131" t="s">
-        <v>24</v>
+        <v>248</v>
       </c>
       <c r="F131" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="G131" s="1"/>
     </row>
@@ -3982,10 +3975,10 @@
         <v>1</v>
       </c>
       <c r="E132" t="s">
-        <v>22</v>
+        <v>242</v>
       </c>
       <c r="F132" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="G132" s="1"/>
     </row>
@@ -4003,10 +3996,10 @@
         <v>1</v>
       </c>
       <c r="E133" t="s">
-        <v>22</v>
+        <v>242</v>
       </c>
       <c r="F133" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="G133" s="1"/>
     </row>
@@ -4024,10 +4017,10 @@
         <v>1</v>
       </c>
       <c r="E134" t="s">
-        <v>24</v>
+        <v>248</v>
       </c>
       <c r="F134" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="G134" s="1"/>
     </row>
@@ -4045,10 +4038,10 @@
         <v>1</v>
       </c>
       <c r="E135" t="s">
-        <v>54</v>
+        <v>252</v>
       </c>
       <c r="F135" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="G135" s="1"/>
     </row>
@@ -4066,10 +4059,10 @@
         <v>1</v>
       </c>
       <c r="E136" t="s">
-        <v>18</v>
+        <v>240</v>
       </c>
       <c r="F136" t="s">
-        <v>120</v>
+        <v>249</v>
       </c>
       <c r="G136" s="1"/>
     </row>
@@ -4087,10 +4080,10 @@
         <v>1</v>
       </c>
       <c r="E137" t="s">
-        <v>16</v>
+        <v>243</v>
       </c>
       <c r="F137" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="G137" s="1"/>
     </row>
@@ -4108,10 +4101,10 @@
         <v>1</v>
       </c>
       <c r="E138" t="s">
-        <v>22</v>
+        <v>242</v>
       </c>
       <c r="F138" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="G138" s="1"/>
     </row>
@@ -4129,10 +4122,10 @@
         <v>1</v>
       </c>
       <c r="E139" t="s">
-        <v>18</v>
+        <v>240</v>
       </c>
       <c r="F139" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="G139" s="1"/>
     </row>
@@ -4150,10 +4143,10 @@
         <v>1</v>
       </c>
       <c r="E140" t="s">
-        <v>20</v>
+        <v>246</v>
       </c>
       <c r="F140" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="G140" s="1"/>
     </row>
@@ -4171,10 +4164,10 @@
         <v>1</v>
       </c>
       <c r="E141" t="s">
-        <v>24</v>
+        <v>248</v>
       </c>
       <c r="F141" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="G141" s="1"/>
     </row>
@@ -4192,10 +4185,10 @@
         <v>1</v>
       </c>
       <c r="E142" t="s">
-        <v>20</v>
+        <v>246</v>
       </c>
       <c r="F142" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="G142" s="1"/>
     </row>
@@ -4213,10 +4206,10 @@
         <v>1</v>
       </c>
       <c r="E143" t="s">
-        <v>54</v>
+        <v>252</v>
       </c>
       <c r="F143" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="G143" s="1"/>
     </row>
@@ -4234,10 +4227,10 @@
         <v>1</v>
       </c>
       <c r="E144" t="s">
-        <v>54</v>
+        <v>252</v>
       </c>
       <c r="F144" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="G144" s="1"/>
     </row>
@@ -4255,10 +4248,10 @@
         <v>1</v>
       </c>
       <c r="E145" t="s">
-        <v>20</v>
+        <v>246</v>
       </c>
       <c r="F145" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="G145" s="1"/>
     </row>
@@ -4276,10 +4269,10 @@
         <v>1</v>
       </c>
       <c r="E146" t="s">
-        <v>18</v>
+        <v>240</v>
       </c>
       <c r="F146" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="G146" s="1"/>
     </row>
@@ -4297,10 +4290,10 @@
         <v>1</v>
       </c>
       <c r="E147" t="s">
-        <v>22</v>
+        <v>242</v>
       </c>
       <c r="F147" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="G147" s="1"/>
     </row>
@@ -4318,10 +4311,10 @@
         <v>1</v>
       </c>
       <c r="E148" t="s">
-        <v>54</v>
+        <v>252</v>
       </c>
       <c r="F148" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="G148" s="1"/>
     </row>
@@ -4339,10 +4332,10 @@
         <v>1</v>
       </c>
       <c r="E149" t="s">
-        <v>20</v>
+        <v>246</v>
       </c>
       <c r="F149" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="G149" s="1"/>
     </row>
@@ -4360,10 +4353,10 @@
         <v>1</v>
       </c>
       <c r="E150" t="s">
-        <v>24</v>
+        <v>248</v>
       </c>
       <c r="F150" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="G150" s="1"/>
     </row>
@@ -4381,10 +4374,10 @@
         <v>1</v>
       </c>
       <c r="E151" t="s">
-        <v>20</v>
+        <v>246</v>
       </c>
       <c r="F151" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="G151" s="1"/>
     </row>
@@ -4402,10 +4395,10 @@
         <v>1</v>
       </c>
       <c r="E152" t="s">
-        <v>22</v>
+        <v>242</v>
       </c>
       <c r="F152" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="G152" s="1"/>
     </row>
@@ -4423,10 +4416,10 @@
         <v>1</v>
       </c>
       <c r="E153" t="s">
-        <v>14</v>
+        <v>251</v>
       </c>
       <c r="F153" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="G153" s="1"/>
     </row>
@@ -4444,10 +4437,10 @@
         <v>1</v>
       </c>
       <c r="E154" t="s">
-        <v>20</v>
+        <v>246</v>
       </c>
       <c r="F154" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="G154" s="1"/>
     </row>
@@ -4465,10 +4458,10 @@
         <v>1</v>
       </c>
       <c r="E155" t="s">
-        <v>24</v>
+        <v>248</v>
       </c>
       <c r="F155" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="G155" s="1"/>
     </row>
@@ -4486,10 +4479,10 @@
         <v>1</v>
       </c>
       <c r="E156" t="s">
-        <v>14</v>
+        <v>251</v>
       </c>
       <c r="F156" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="G156" s="1"/>
     </row>
@@ -4507,10 +4500,10 @@
         <v>1</v>
       </c>
       <c r="E157" t="s">
-        <v>20</v>
+        <v>246</v>
       </c>
       <c r="F157" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="G157" s="1"/>
     </row>
@@ -4528,10 +4521,10 @@
         <v>1</v>
       </c>
       <c r="E158" t="s">
-        <v>22</v>
+        <v>242</v>
       </c>
       <c r="F158" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="G158" s="1"/>
     </row>
@@ -4549,10 +4542,10 @@
         <v>1</v>
       </c>
       <c r="E159" t="s">
-        <v>31</v>
+        <v>240</v>
       </c>
       <c r="F159" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="G159" s="1"/>
     </row>
@@ -4570,10 +4563,10 @@
         <v>1</v>
       </c>
       <c r="E160" t="s">
-        <v>16</v>
+        <v>243</v>
       </c>
       <c r="F160" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="G160" s="1"/>
     </row>
@@ -4591,10 +4584,10 @@
         <v>1</v>
       </c>
       <c r="E161" t="s">
-        <v>18</v>
+        <v>240</v>
       </c>
       <c r="F161" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G161" s="1"/>
     </row>
@@ -4612,10 +4605,10 @@
         <v>1</v>
       </c>
       <c r="E162" t="s">
-        <v>16</v>
+        <v>243</v>
       </c>
       <c r="F162" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G162" s="1"/>
     </row>
@@ -4633,10 +4626,10 @@
         <v>1</v>
       </c>
       <c r="E163" t="s">
-        <v>18</v>
+        <v>240</v>
       </c>
       <c r="F163" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G163" s="1"/>
     </row>
@@ -4654,10 +4647,10 @@
         <v>1</v>
       </c>
       <c r="E164" t="s">
-        <v>14</v>
+        <v>251</v>
       </c>
       <c r="F164" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G164" s="1"/>
     </row>
@@ -4675,10 +4668,10 @@
         <v>1</v>
       </c>
       <c r="E165" t="s">
-        <v>14</v>
+        <v>251</v>
       </c>
       <c r="F165" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="G165" s="1"/>
     </row>
@@ -4696,10 +4689,10 @@
         <v>1</v>
       </c>
       <c r="E166" t="s">
-        <v>18</v>
+        <v>240</v>
       </c>
       <c r="F166" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G166" s="1"/>
     </row>
@@ -4717,10 +4710,10 @@
         <v>1</v>
       </c>
       <c r="E167" t="s">
-        <v>20</v>
+        <v>246</v>
       </c>
       <c r="F167" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G167" s="1"/>
     </row>
@@ -4738,10 +4731,10 @@
         <v>1</v>
       </c>
       <c r="E168" t="s">
-        <v>24</v>
+        <v>248</v>
       </c>
       <c r="F168" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G168" s="1"/>
     </row>
@@ -4759,10 +4752,10 @@
         <v>1</v>
       </c>
       <c r="E169" t="s">
-        <v>24</v>
+        <v>248</v>
       </c>
       <c r="F169" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="G169" s="1"/>
     </row>
@@ -4780,10 +4773,10 @@
         <v>1</v>
       </c>
       <c r="E170" t="s">
-        <v>24</v>
+        <v>248</v>
       </c>
       <c r="F170" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="G170" s="1"/>
     </row>
@@ -4801,10 +4794,10 @@
         <v>1</v>
       </c>
       <c r="E171" t="s">
-        <v>31</v>
+        <v>240</v>
       </c>
       <c r="F171" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="G171" s="1"/>
     </row>
@@ -4822,10 +4815,10 @@
         <v>1</v>
       </c>
       <c r="E172" t="s">
-        <v>14</v>
+        <v>251</v>
       </c>
       <c r="F172" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="G172" s="1"/>
     </row>
@@ -4843,10 +4836,10 @@
         <v>1</v>
       </c>
       <c r="E173" t="s">
-        <v>18</v>
+        <v>240</v>
       </c>
       <c r="F173" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="G173" s="1"/>
     </row>
@@ -4864,10 +4857,10 @@
         <v>1</v>
       </c>
       <c r="E174" t="s">
-        <v>31</v>
+        <v>240</v>
       </c>
       <c r="F174" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="G174" s="1"/>
     </row>
@@ -4885,10 +4878,10 @@
         <v>1</v>
       </c>
       <c r="E175" t="s">
-        <v>22</v>
+        <v>242</v>
       </c>
       <c r="F175" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="G175" s="1"/>
     </row>
@@ -4906,10 +4899,10 @@
         <v>1</v>
       </c>
       <c r="E176" t="s">
-        <v>18</v>
+        <v>240</v>
       </c>
       <c r="F176" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="G176" s="1"/>
     </row>
@@ -4927,10 +4920,10 @@
         <v>1</v>
       </c>
       <c r="E177" t="s">
-        <v>18</v>
+        <v>240</v>
       </c>
       <c r="F177" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="G177" s="1"/>
     </row>
@@ -4948,10 +4941,10 @@
         <v>1</v>
       </c>
       <c r="E178" t="s">
-        <v>18</v>
+        <v>240</v>
       </c>
       <c r="F178" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="G178" s="1"/>
     </row>
@@ -4969,10 +4962,10 @@
         <v>1</v>
       </c>
       <c r="E179" t="s">
-        <v>22</v>
+        <v>242</v>
       </c>
       <c r="F179" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="G179" s="1"/>
     </row>
@@ -4990,10 +4983,10 @@
         <v>1</v>
       </c>
       <c r="E180" t="s">
-        <v>14</v>
+        <v>251</v>
       </c>
       <c r="F180" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="G180" s="1"/>
     </row>
@@ -5011,10 +5004,10 @@
         <v>1</v>
       </c>
       <c r="E181" t="s">
-        <v>20</v>
+        <v>246</v>
       </c>
       <c r="F181" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="G181" s="1"/>
     </row>
@@ -5032,10 +5025,10 @@
         <v>1</v>
       </c>
       <c r="E182" t="s">
-        <v>18</v>
+        <v>240</v>
       </c>
       <c r="F182" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="G182" s="1"/>
     </row>
@@ -5053,10 +5046,10 @@
         <v>1</v>
       </c>
       <c r="E183" t="s">
-        <v>54</v>
+        <v>252</v>
       </c>
       <c r="F183" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="G183" s="1"/>
     </row>
@@ -5074,10 +5067,10 @@
         <v>1</v>
       </c>
       <c r="E184" t="s">
-        <v>54</v>
+        <v>252</v>
       </c>
       <c r="F184" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="G184" s="1"/>
     </row>
@@ -5095,10 +5088,10 @@
         <v>1</v>
       </c>
       <c r="E185" t="s">
-        <v>22</v>
+        <v>242</v>
       </c>
       <c r="F185" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="G185" s="1"/>
     </row>
@@ -5116,10 +5109,10 @@
         <v>1</v>
       </c>
       <c r="E186" t="s">
-        <v>20</v>
+        <v>246</v>
       </c>
       <c r="F186" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="G186" s="1"/>
     </row>
@@ -5137,10 +5130,10 @@
         <v>1</v>
       </c>
       <c r="E187" t="s">
-        <v>14</v>
+        <v>251</v>
       </c>
       <c r="F187" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="G187" s="1"/>
     </row>
@@ -5158,10 +5151,10 @@
         <v>1</v>
       </c>
       <c r="E188" t="s">
-        <v>22</v>
+        <v>242</v>
       </c>
       <c r="F188" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="G188" s="1"/>
     </row>
@@ -5179,10 +5172,10 @@
         <v>1</v>
       </c>
       <c r="E189" t="s">
-        <v>14</v>
+        <v>251</v>
       </c>
       <c r="F189" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="G189" s="1"/>
     </row>
@@ -5200,10 +5193,10 @@
         <v>1</v>
       </c>
       <c r="E190" t="s">
-        <v>20</v>
+        <v>246</v>
       </c>
       <c r="F190" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="G190" s="1"/>
     </row>
@@ -5221,10 +5214,10 @@
         <v>1</v>
       </c>
       <c r="E191" t="s">
-        <v>18</v>
+        <v>240</v>
       </c>
       <c r="F191" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="G191" s="1"/>
     </row>
@@ -5242,10 +5235,10 @@
         <v>1</v>
       </c>
       <c r="E192" t="s">
-        <v>14</v>
+        <v>251</v>
       </c>
       <c r="F192" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="G192" s="1"/>
     </row>
@@ -5263,10 +5256,10 @@
         <v>1</v>
       </c>
       <c r="E193" t="s">
-        <v>20</v>
+        <v>246</v>
       </c>
       <c r="F193" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="G193" s="1"/>
     </row>
@@ -5284,10 +5277,10 @@
         <v>1</v>
       </c>
       <c r="E194" t="s">
-        <v>22</v>
+        <v>242</v>
       </c>
       <c r="F194" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="G194" s="1"/>
     </row>
@@ -5305,10 +5298,10 @@
         <v>1</v>
       </c>
       <c r="E195" t="s">
-        <v>20</v>
+        <v>246</v>
       </c>
       <c r="F195" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="G195" s="1"/>
     </row>
@@ -5326,10 +5319,10 @@
         <v>1</v>
       </c>
       <c r="E196" t="s">
-        <v>31</v>
+        <v>240</v>
       </c>
       <c r="F196" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G196" s="1"/>
     </row>
@@ -5347,10 +5340,10 @@
         <v>1</v>
       </c>
       <c r="E197" t="s">
-        <v>18</v>
+        <v>240</v>
       </c>
       <c r="F197" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="G197" s="1"/>
     </row>
@@ -5368,10 +5361,10 @@
         <v>1</v>
       </c>
       <c r="E198" t="s">
-        <v>14</v>
+        <v>251</v>
       </c>
       <c r="F198" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="G198" s="1"/>
     </row>
@@ -5389,10 +5382,10 @@
         <v>1</v>
       </c>
       <c r="E199" t="s">
-        <v>22</v>
+        <v>242</v>
       </c>
       <c r="F199" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="G199" s="1"/>
     </row>
@@ -5410,10 +5403,10 @@
         <v>1</v>
       </c>
       <c r="E200" t="s">
-        <v>20</v>
+        <v>246</v>
       </c>
       <c r="F200" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="G200" s="1"/>
     </row>
@@ -5431,10 +5424,10 @@
         <v>1</v>
       </c>
       <c r="E201" t="s">
-        <v>18</v>
+        <v>240</v>
       </c>
       <c r="F201" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="G201" s="1"/>
     </row>
@@ -5452,10 +5445,10 @@
         <v>1</v>
       </c>
       <c r="E202" t="s">
-        <v>54</v>
+        <v>252</v>
       </c>
       <c r="F202" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="G202" s="1"/>
     </row>
@@ -5473,10 +5466,10 @@
         <v>1</v>
       </c>
       <c r="E203" t="s">
-        <v>22</v>
+        <v>242</v>
       </c>
       <c r="F203" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="G203" s="1"/>
     </row>
@@ -5494,10 +5487,10 @@
         <v>1</v>
       </c>
       <c r="E204" t="s">
-        <v>31</v>
+        <v>240</v>
       </c>
       <c r="F204" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="G204" s="1"/>
     </row>
@@ -5515,10 +5508,10 @@
         <v>1</v>
       </c>
       <c r="E205" t="s">
-        <v>14</v>
+        <v>251</v>
       </c>
       <c r="F205" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="G205" s="1"/>
     </row>
@@ -5536,10 +5529,10 @@
         <v>1</v>
       </c>
       <c r="E206" t="s">
-        <v>16</v>
+        <v>243</v>
       </c>
       <c r="F206" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="G206" s="1"/>
     </row>
@@ -5557,10 +5550,10 @@
         <v>1</v>
       </c>
       <c r="E207" t="s">
-        <v>22</v>
+        <v>242</v>
       </c>
       <c r="F207" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="G207" s="1"/>
     </row>
@@ -5578,10 +5571,10 @@
         <v>1</v>
       </c>
       <c r="E208" t="s">
-        <v>22</v>
+        <v>242</v>
       </c>
       <c r="F208" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="G208" s="1"/>
     </row>
@@ -5599,10 +5592,10 @@
         <v>1</v>
       </c>
       <c r="E209" t="s">
-        <v>18</v>
+        <v>240</v>
       </c>
       <c r="F209" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="G209" s="1"/>
     </row>
@@ -5620,10 +5613,10 @@
         <v>1</v>
       </c>
       <c r="E210" t="s">
-        <v>18</v>
+        <v>240</v>
       </c>
       <c r="F210" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="G210" s="1"/>
     </row>
@@ -5641,10 +5634,10 @@
         <v>1</v>
       </c>
       <c r="E211" t="s">
-        <v>20</v>
+        <v>246</v>
       </c>
       <c r="F211" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="G211" s="1"/>
     </row>
@@ -5662,10 +5655,10 @@
         <v>1</v>
       </c>
       <c r="E212" t="s">
-        <v>20</v>
+        <v>246</v>
       </c>
       <c r="F212" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="G212" s="1"/>
     </row>
@@ -5683,10 +5676,10 @@
         <v>1</v>
       </c>
       <c r="E213" t="s">
-        <v>20</v>
+        <v>246</v>
       </c>
       <c r="F213" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G213" s="1"/>
     </row>
@@ -5704,10 +5697,10 @@
         <v>1</v>
       </c>
       <c r="E214" t="s">
-        <v>18</v>
+        <v>240</v>
       </c>
       <c r="F214" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="G214" s="1"/>
     </row>
@@ -5725,10 +5718,10 @@
         <v>1</v>
       </c>
       <c r="E215" t="s">
-        <v>24</v>
+        <v>248</v>
       </c>
       <c r="F215" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="G215" s="1"/>
     </row>
@@ -5746,10 +5739,10 @@
         <v>1</v>
       </c>
       <c r="E216" t="s">
-        <v>20</v>
+        <v>246</v>
       </c>
       <c r="F216" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="G216" s="1"/>
     </row>
@@ -5767,10 +5760,10 @@
         <v>1</v>
       </c>
       <c r="E217" t="s">
-        <v>24</v>
+        <v>248</v>
       </c>
       <c r="F217" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="G217" s="1"/>
     </row>
@@ -5788,10 +5781,10 @@
         <v>1</v>
       </c>
       <c r="E218" t="s">
-        <v>18</v>
+        <v>240</v>
       </c>
       <c r="F218" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="G218" s="1"/>
     </row>
@@ -5809,10 +5802,10 @@
         <v>1</v>
       </c>
       <c r="E219" t="s">
-        <v>14</v>
+        <v>251</v>
       </c>
       <c r="F219" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="G219" s="1"/>
     </row>
@@ -5830,10 +5823,10 @@
         <v>1</v>
       </c>
       <c r="E220" t="s">
-        <v>20</v>
+        <v>246</v>
       </c>
       <c r="F220" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="G220" s="1"/>
     </row>
@@ -5851,10 +5844,10 @@
         <v>1</v>
       </c>
       <c r="E221" t="s">
-        <v>20</v>
+        <v>246</v>
       </c>
       <c r="F221" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="G221" s="1"/>
     </row>
@@ -5872,10 +5865,10 @@
         <v>1</v>
       </c>
       <c r="E222" t="s">
+        <v>242</v>
+      </c>
+      <c r="F222" t="s">
         <v>22</v>
-      </c>
-      <c r="F222" t="s">
-        <v>33</v>
       </c>
       <c r="G222" s="1"/>
     </row>
@@ -5893,10 +5886,10 @@
         <v>1</v>
       </c>
       <c r="E223" t="s">
-        <v>18</v>
+        <v>240</v>
       </c>
       <c r="F223" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="G223" s="1"/>
     </row>
@@ -5914,10 +5907,10 @@
         <v>1</v>
       </c>
       <c r="E224" t="s">
-        <v>31</v>
+        <v>240</v>
       </c>
       <c r="F224" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G224" s="1"/>
     </row>
@@ -5935,10 +5928,10 @@
         <v>1</v>
       </c>
       <c r="E225" t="s">
-        <v>16</v>
+        <v>243</v>
       </c>
       <c r="F225" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="G225" s="1"/>
     </row>
@@ -5956,10 +5949,10 @@
         <v>1</v>
       </c>
       <c r="E226" t="s">
-        <v>20</v>
+        <v>246</v>
       </c>
       <c r="F226" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="G226" s="1"/>
     </row>
@@ -5977,10 +5970,10 @@
         <v>1</v>
       </c>
       <c r="E227" t="s">
-        <v>22</v>
+        <v>242</v>
       </c>
       <c r="F227" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="G227" s="1"/>
     </row>
@@ -5998,10 +5991,10 @@
         <v>1</v>
       </c>
       <c r="E228" t="s">
-        <v>14</v>
+        <v>251</v>
       </c>
       <c r="F228" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="G228" s="1"/>
     </row>
@@ -6019,10 +6012,10 @@
         <v>1</v>
       </c>
       <c r="E229" t="s">
-        <v>22</v>
+        <v>242</v>
       </c>
       <c r="F229" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G229" s="1"/>
     </row>
@@ -6040,10 +6033,10 @@
         <v>1</v>
       </c>
       <c r="E230" t="s">
-        <v>24</v>
+        <v>248</v>
       </c>
       <c r="F230" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="G230" s="1"/>
     </row>
@@ -6061,10 +6054,10 @@
         <v>1</v>
       </c>
       <c r="E231" t="s">
-        <v>22</v>
+        <v>242</v>
       </c>
       <c r="F231" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="G231" s="1"/>
     </row>
@@ -6082,10 +6075,10 @@
         <v>1</v>
       </c>
       <c r="E232" t="s">
-        <v>20</v>
+        <v>246</v>
       </c>
       <c r="F232" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G232" s="1"/>
     </row>
@@ -6103,10 +6096,10 @@
         <v>1</v>
       </c>
       <c r="E233" t="s">
-        <v>18</v>
+        <v>240</v>
       </c>
       <c r="F233" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G233" s="1"/>
     </row>
@@ -6124,10 +6117,10 @@
         <v>1</v>
       </c>
       <c r="E234" t="s">
-        <v>16</v>
+        <v>243</v>
       </c>
       <c r="F234" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G234" s="1"/>
     </row>
@@ -6145,10 +6138,10 @@
         <v>1</v>
       </c>
       <c r="E235" t="s">
-        <v>14</v>
+        <v>251</v>
       </c>
       <c r="F235" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G235" s="1"/>
     </row>
